--- a/光伏配储项目/电价数据/2026/两英站.xlsx
+++ b/光伏配储项目/电价数据/2026/两英站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33079</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.50127</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24141</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07279000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25641</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24107</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.46984</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.51263</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.85805</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.96945</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58357</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.94964</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.04898</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.87676</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.76407</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8050499999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.96262</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5153099999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08843</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.26819</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.52844</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.51004</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34373</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.53987</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.9410499999999999</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.59785</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.26167</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.60809</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.44738</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.43596</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6506799999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61146</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.67959</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.55844</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.7586799999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5340499999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.57602</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.5368999999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.30009</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.84657</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.9603700000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.69374</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.90012</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.9992300000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.9558300000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.88462</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7396200000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78696</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.71497</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8284</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75136</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.85939</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.72677</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.2819</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.6739299999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.65925</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33207</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.14925</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19256</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.10263</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.53692</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.52598</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.62585</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.62418</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.68862</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.6327200000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.68225</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.69901</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7320599999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.46791</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.66173</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6380800000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.55703</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4914</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.12921</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45833</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51184</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52444</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5812</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.62518</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.56894</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.64376</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.71163</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.5438999999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5137200000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52665</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.50651</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6622100000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.62042</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6084400000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5839500000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56168</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.52615</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.60537</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33882</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44522</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48478</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46796</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.02535</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.79702</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21784</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23081</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.19793</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6697799999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.23084</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14362</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26413</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25668</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23881</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10353</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03004</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31885</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25076</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19829</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.19761</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.10706</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.13798</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22068</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18129</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20803</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.11215</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19425</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06063</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31671</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.1463</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78135</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65961</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5743400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44401</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.48595</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56668</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.77073</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44654</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.24771</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.55849</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26757</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.26513</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.14152</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18592</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32497</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.62975</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.19268</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.23472</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.20035</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.03738</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.06079</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.19879</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.14969</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.20318</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.23306</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.21681</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.21845</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.02064</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.02981</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.01753</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.02793</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.01974</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.03489</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2277</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.21519</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.17641</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.21249</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.20082</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.21361</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.21657</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.1957</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.21268</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.21584</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.22428</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.22126</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.21532</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.20219</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.20105</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.21021</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.20679</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.21306</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.008140000000000001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.12097</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.62637</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.006030000000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.14104</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.12923</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.009890000000000001</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.12312</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.15297</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.15581</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.13388</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.22536</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.23239</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.20945</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.25101</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.26208</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.24747</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.22633</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.22801</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.22471</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.07228</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.25099</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.00919</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.22079</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.24194</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.19464</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.10394</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2016</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.23578</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.16219</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.07572</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.23926</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.23514</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.03927000000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.09803000000000001</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.21394</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.10661</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.02878</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.08313</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.18787</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.26629</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.26251</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.25768</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.24752</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.21682</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.22527</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.25462</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.22602</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.47316</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.24453</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.17951</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.21903</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.20323</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.19152</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.11326</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.15305</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19405</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19119</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.12247</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.18423</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.20148</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.19936</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.22989</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.01351</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.00271</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.08120999999999999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.08704000000000001</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.22301</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03514</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.008359999999999999</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19729</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.03574</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.05429</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.05298</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2131</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.19419</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.06805</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.23699</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.12724</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.02409</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.19884</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.19952</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.20866</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.22883</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.21401</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22328</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.20241</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.23929</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.25099</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25772</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.22023</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24752</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.27798</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27928</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25397</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28455</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25174</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3027</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.7661699999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.5303099999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49405</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.46663</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5134299999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45677</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.19574</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6888500000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.15807</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.24577</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.20743</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.14985</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27886</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20559</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19754</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27411</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19671</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16192</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23926</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19644</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.12743</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17547</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16656</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.19694</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22456</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.27354</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.27454</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24439</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.26588</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.24697</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.24501</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.25988</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.26577</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.11689</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.10109</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23982</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31998</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21374</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29895</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50503</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.50936</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.48426</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6449900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31643</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42814</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5816399999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6689700000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.60426</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48339</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.54452</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.46839</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64398</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32342</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01568</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.61705</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.14488</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.18306</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.12208</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.11872</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.13103</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.18934</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.17147</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.12779</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.12281</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.07029000000000001</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.12637</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.11861</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.11423</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.15983</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.23055</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17546</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25614</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17567</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.2069</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17449</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.009650000000000001</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16468</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16975</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17539</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.008449999999999999</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18669</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18822</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15688</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03121</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.19377</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.21914</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.23781</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.17382</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23889</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24407</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.24262</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.14035</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.15266</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25208</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.20819</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24594</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.14572</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.15515</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24616</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.13052</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.11845</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.17531</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23306</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.26037</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05453</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18785</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20674</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22689</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21881</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01069</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00191</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00191</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20144</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01121</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00191</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18167</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01068</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01068</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00352</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24578</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03797</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00614</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.02194</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25347</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.15688</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.23915</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25272</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25751</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.00317</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26934</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27186</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27283</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03588</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17822</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17717</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17445</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.01837</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17042</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15892</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.01742</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.01998</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.01702</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01281</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01684</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41611</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20266</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.01979</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04165</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85894</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86173</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09297</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25131</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.46236</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00159</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06877</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.5557799999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.61021</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.68303</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.20024</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.58453</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.5827599999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.63646</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3109</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20046</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25176</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22113</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20894</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17562</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20442</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16992</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17269</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.01891</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16849</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19095</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29479</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.47181</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.59878</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6259400000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.55525</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.62702</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6929299999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42866</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20328</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31912</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.57475</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.61172</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.45903</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.8044199999999999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.63309</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.91928</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53987</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.7019500000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.60742</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.87918</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7957000000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.3531</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5800299999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.52616</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32371</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01928</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.57398</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20044</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.54648</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.25029</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.26895</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.19187</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.24531</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.52076</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.52625</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.68509</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.53964</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.44208</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.46191</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32792</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.5474600000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.6065900000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.47163</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3396</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14608</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12158</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22598</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18821</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16275</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17089</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20563</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.26044</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36927</v>
       </c>
     </row>
   </sheetData>
